--- a/output_lapsim/fsae_A_2025/fsae_A_2025_track.xlsx
+++ b/output_lapsim/fsae_A_2025/fsae_A_2025_track.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Danny\2_project\ongoing\DXF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Danny\DH3868\map-data-tools\output_lapsim\fsae_A_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBDCE13-8637-41D2-B502-4D703A2EBDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2A4414-FFE5-4B22-886E-90FBE7A1F0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6400" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trackdata" sheetId="1" r:id="rId1"/>
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M1701"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -870,6 +870,9 @@
       <c r="F11">
         <v>164.8507706481096</v>
       </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
       <c r="L11">
         <v>45.811131766684959</v>
       </c>
@@ -1262,6 +1265,9 @@
       <c r="F21">
         <v>232.87919492219581</v>
       </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
       <c r="L21">
         <v>71.593502992911098</v>
       </c>
@@ -2023,6 +2029,9 @@
       <c r="F40">
         <v>152.635279918523</v>
       </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
       <c r="L40">
         <v>22.608961167815419</v>
       </c>
@@ -2825,6 +2834,9 @@
       <c r="F60">
         <v>31.44385433138719</v>
       </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
       <c r="L60">
         <v>35.526958566448513</v>
       </c>
@@ -3781,6 +3793,1163 @@
         <v>1209.3086493226922</v>
       </c>
     </row>
+    <row r="97" customFormat="1"/>
+    <row r="98" customFormat="1"/>
+    <row r="99" customFormat="1"/>
+    <row r="100" customFormat="1"/>
+    <row r="101" customFormat="1"/>
+    <row r="102" customFormat="1"/>
+    <row r="103" customFormat="1"/>
+    <row r="104" customFormat="1"/>
+    <row r="105" customFormat="1"/>
+    <row r="106" customFormat="1"/>
+    <row r="107" customFormat="1"/>
+    <row r="108" customFormat="1"/>
+    <row r="109" customFormat="1"/>
+    <row r="110" customFormat="1"/>
+    <row r="111" customFormat="1"/>
+    <row r="112" customFormat="1"/>
+    <row r="113" customFormat="1"/>
+    <row r="114" customFormat="1"/>
+    <row r="115" customFormat="1"/>
+    <row r="116" customFormat="1"/>
+    <row r="117" customFormat="1"/>
+    <row r="118" customFormat="1"/>
+    <row r="119" customFormat="1"/>
+    <row r="120" customFormat="1"/>
+    <row r="121" customFormat="1"/>
+    <row r="122" customFormat="1"/>
+    <row r="123" customFormat="1"/>
+    <row r="124" customFormat="1"/>
+    <row r="125" customFormat="1"/>
+    <row r="126" customFormat="1"/>
+    <row r="127" customFormat="1"/>
+    <row r="128" customFormat="1"/>
+    <row r="129" customFormat="1"/>
+    <row r="130" customFormat="1"/>
+    <row r="131" customFormat="1"/>
+    <row r="132" customFormat="1"/>
+    <row r="133" customFormat="1"/>
+    <row r="134" customFormat="1"/>
+    <row r="135" customFormat="1"/>
+    <row r="136" customFormat="1"/>
+    <row r="137" customFormat="1"/>
+    <row r="138" customFormat="1"/>
+    <row r="139" customFormat="1"/>
+    <row r="140" customFormat="1"/>
+    <row r="141" customFormat="1"/>
+    <row r="142" customFormat="1"/>
+    <row r="143" customFormat="1"/>
+    <row r="144" customFormat="1"/>
+    <row r="145" customFormat="1"/>
+    <row r="146" customFormat="1"/>
+    <row r="147" customFormat="1"/>
+    <row r="148" customFormat="1"/>
+    <row r="149" customFormat="1"/>
+    <row r="150" customFormat="1"/>
+    <row r="151" customFormat="1"/>
+    <row r="152" customFormat="1"/>
+    <row r="153" customFormat="1"/>
+    <row r="154" customFormat="1"/>
+    <row r="155" customFormat="1"/>
+    <row r="156" customFormat="1"/>
+    <row r="157" customFormat="1"/>
+    <row r="158" customFormat="1"/>
+    <row r="159" customFormat="1"/>
+    <row r="160" customFormat="1"/>
+    <row r="161" customFormat="1"/>
+    <row r="162" customFormat="1"/>
+    <row r="163" customFormat="1"/>
+    <row r="164" customFormat="1"/>
+    <row r="165" customFormat="1"/>
+    <row r="166" customFormat="1"/>
+    <row r="167" customFormat="1"/>
+    <row r="168" customFormat="1"/>
+    <row r="169" customFormat="1"/>
+    <row r="170" customFormat="1"/>
+    <row r="171" customFormat="1"/>
+    <row r="172" customFormat="1"/>
+    <row r="173" customFormat="1"/>
+    <row r="174" customFormat="1"/>
+    <row r="175" customFormat="1"/>
+    <row r="176" customFormat="1"/>
+    <row r="177" customFormat="1"/>
+    <row r="178" customFormat="1"/>
+    <row r="179" customFormat="1"/>
+    <row r="180" customFormat="1"/>
+    <row r="181" customFormat="1"/>
+    <row r="182" customFormat="1"/>
+    <row r="183" customFormat="1"/>
+    <row r="184" customFormat="1"/>
+    <row r="185" customFormat="1"/>
+    <row r="186" customFormat="1"/>
+    <row r="187" customFormat="1"/>
+    <row r="188" customFormat="1"/>
+    <row r="189" customFormat="1"/>
+    <row r="190" customFormat="1"/>
+    <row r="191" customFormat="1"/>
+    <row r="192" customFormat="1"/>
+    <row r="193" customFormat="1"/>
+    <row r="194" customFormat="1"/>
+    <row r="195" customFormat="1"/>
+    <row r="196" customFormat="1"/>
+    <row r="197" customFormat="1"/>
+    <row r="198" customFormat="1"/>
+    <row r="199" customFormat="1"/>
+    <row r="200" customFormat="1"/>
+    <row r="201" customFormat="1"/>
+    <row r="202" customFormat="1"/>
+    <row r="203" customFormat="1"/>
+    <row r="204" customFormat="1"/>
+    <row r="205" customFormat="1"/>
+    <row r="206" customFormat="1"/>
+    <row r="207" customFormat="1"/>
+    <row r="208" customFormat="1"/>
+    <row r="209" customFormat="1"/>
+    <row r="210" customFormat="1"/>
+    <row r="211" customFormat="1"/>
+    <row r="212" customFormat="1"/>
+    <row r="213" customFormat="1"/>
+    <row r="214" customFormat="1"/>
+    <row r="215" customFormat="1"/>
+    <row r="216" customFormat="1"/>
+    <row r="217" customFormat="1"/>
+    <row r="218" customFormat="1"/>
+    <row r="219" customFormat="1"/>
+    <row r="220" customFormat="1"/>
+    <row r="221" customFormat="1"/>
+    <row r="222" customFormat="1"/>
+    <row r="223" customFormat="1"/>
+    <row r="224" customFormat="1"/>
+    <row r="225" customFormat="1"/>
+    <row r="226" customFormat="1"/>
+    <row r="227" customFormat="1"/>
+    <row r="228" customFormat="1"/>
+    <row r="229" customFormat="1"/>
+    <row r="230" customFormat="1"/>
+    <row r="231" customFormat="1"/>
+    <row r="232" customFormat="1"/>
+    <row r="233" customFormat="1"/>
+    <row r="234" customFormat="1"/>
+    <row r="235" customFormat="1"/>
+    <row r="236" customFormat="1"/>
+    <row r="237" customFormat="1"/>
+    <row r="238" customFormat="1"/>
+    <row r="239" customFormat="1"/>
+    <row r="240" customFormat="1"/>
+    <row r="241" customFormat="1"/>
+    <row r="242" customFormat="1"/>
+    <row r="243" customFormat="1"/>
+    <row r="244" customFormat="1"/>
+    <row r="245" customFormat="1"/>
+    <row r="246" customFormat="1"/>
+    <row r="247" customFormat="1"/>
+    <row r="248" customFormat="1"/>
+    <row r="249" customFormat="1"/>
+    <row r="250" customFormat="1"/>
+    <row r="251" customFormat="1"/>
+    <row r="252" customFormat="1"/>
+    <row r="253" customFormat="1"/>
+    <row r="254" customFormat="1"/>
+    <row r="255" customFormat="1"/>
+    <row r="256" customFormat="1"/>
+    <row r="257" customFormat="1"/>
+    <row r="258" customFormat="1"/>
+    <row r="259" customFormat="1"/>
+    <row r="260" customFormat="1"/>
+    <row r="261" customFormat="1"/>
+    <row r="262" customFormat="1"/>
+    <row r="263" customFormat="1"/>
+    <row r="264" customFormat="1"/>
+    <row r="265" customFormat="1"/>
+    <row r="266" customFormat="1"/>
+    <row r="267" customFormat="1"/>
+    <row r="268" customFormat="1"/>
+    <row r="269" customFormat="1"/>
+    <row r="270" customFormat="1"/>
+    <row r="271" customFormat="1"/>
+    <row r="272" customFormat="1"/>
+    <row r="273" customFormat="1"/>
+    <row r="274" customFormat="1"/>
+    <row r="275" customFormat="1"/>
+    <row r="276" customFormat="1"/>
+    <row r="277" customFormat="1"/>
+    <row r="278" customFormat="1"/>
+    <row r="279" customFormat="1"/>
+    <row r="280" customFormat="1"/>
+    <row r="281" customFormat="1"/>
+    <row r="282" customFormat="1"/>
+    <row r="283" customFormat="1"/>
+    <row r="284" customFormat="1"/>
+    <row r="285" customFormat="1"/>
+    <row r="286" customFormat="1"/>
+    <row r="287" customFormat="1"/>
+    <row r="288" customFormat="1"/>
+    <row r="289" customFormat="1"/>
+    <row r="290" customFormat="1"/>
+    <row r="291" customFormat="1"/>
+    <row r="292" customFormat="1"/>
+    <row r="293" customFormat="1"/>
+    <row r="294" customFormat="1"/>
+    <row r="295" customFormat="1"/>
+    <row r="296" customFormat="1"/>
+    <row r="297" customFormat="1"/>
+    <row r="298" customFormat="1"/>
+    <row r="299" customFormat="1"/>
+    <row r="300" customFormat="1"/>
+    <row r="301" customFormat="1"/>
+    <row r="302" customFormat="1"/>
+    <row r="303" customFormat="1"/>
+    <row r="304" customFormat="1"/>
+    <row r="305" customFormat="1"/>
+    <row r="306" customFormat="1"/>
+    <row r="307" customFormat="1"/>
+    <row r="308" customFormat="1"/>
+    <row r="309" customFormat="1"/>
+    <row r="310" customFormat="1"/>
+    <row r="311" customFormat="1"/>
+    <row r="312" customFormat="1"/>
+    <row r="313" customFormat="1"/>
+    <row r="314" customFormat="1"/>
+    <row r="315" customFormat="1"/>
+    <row r="316" customFormat="1"/>
+    <row r="317" customFormat="1"/>
+    <row r="318" customFormat="1"/>
+    <row r="319" customFormat="1"/>
+    <row r="320" customFormat="1"/>
+    <row r="321" customFormat="1"/>
+    <row r="322" customFormat="1"/>
+    <row r="323" customFormat="1"/>
+    <row r="324" customFormat="1"/>
+    <row r="325" customFormat="1"/>
+    <row r="326" customFormat="1"/>
+    <row r="327" customFormat="1"/>
+    <row r="328" customFormat="1"/>
+    <row r="329" customFormat="1"/>
+    <row r="330" customFormat="1"/>
+    <row r="331" customFormat="1"/>
+    <row r="332" customFormat="1"/>
+    <row r="333" customFormat="1"/>
+    <row r="334" customFormat="1"/>
+    <row r="335" customFormat="1"/>
+    <row r="336" customFormat="1"/>
+    <row r="337" customFormat="1"/>
+    <row r="338" customFormat="1"/>
+    <row r="339" customFormat="1"/>
+    <row r="340" customFormat="1"/>
+    <row r="341" customFormat="1"/>
+    <row r="342" customFormat="1"/>
+    <row r="343" customFormat="1"/>
+    <row r="344" customFormat="1"/>
+    <row r="345" customFormat="1"/>
+    <row r="346" customFormat="1"/>
+    <row r="347" customFormat="1"/>
+    <row r="348" customFormat="1"/>
+    <row r="349" customFormat="1"/>
+    <row r="350" customFormat="1"/>
+    <row r="351" customFormat="1"/>
+    <row r="352" customFormat="1"/>
+    <row r="353" customFormat="1"/>
+    <row r="354" customFormat="1"/>
+    <row r="355" customFormat="1"/>
+    <row r="356" customFormat="1"/>
+    <row r="357" customFormat="1"/>
+    <row r="358" customFormat="1"/>
+    <row r="359" customFormat="1"/>
+    <row r="360" customFormat="1"/>
+    <row r="361" customFormat="1"/>
+    <row r="362" customFormat="1"/>
+    <row r="363" customFormat="1"/>
+    <row r="364" customFormat="1"/>
+    <row r="365" customFormat="1"/>
+    <row r="366" customFormat="1"/>
+    <row r="367" customFormat="1"/>
+    <row r="368" customFormat="1"/>
+    <row r="369" customFormat="1"/>
+    <row r="370" customFormat="1"/>
+    <row r="371" customFormat="1"/>
+    <row r="372" customFormat="1"/>
+    <row r="373" customFormat="1"/>
+    <row r="374" customFormat="1"/>
+    <row r="375" customFormat="1"/>
+    <row r="376" customFormat="1"/>
+    <row r="377" customFormat="1"/>
+    <row r="378" customFormat="1"/>
+    <row r="379" customFormat="1"/>
+    <row r="380" customFormat="1"/>
+    <row r="381" customFormat="1"/>
+    <row r="382" customFormat="1"/>
+    <row r="383" customFormat="1"/>
+    <row r="384" customFormat="1"/>
+    <row r="385" customFormat="1"/>
+    <row r="386" customFormat="1"/>
+    <row r="387" customFormat="1"/>
+    <row r="388" customFormat="1"/>
+    <row r="389" customFormat="1"/>
+    <row r="390" customFormat="1"/>
+    <row r="391" customFormat="1"/>
+    <row r="392" customFormat="1"/>
+    <row r="393" customFormat="1"/>
+    <row r="394" customFormat="1"/>
+    <row r="395" customFormat="1"/>
+    <row r="396" customFormat="1"/>
+    <row r="397" customFormat="1"/>
+    <row r="398" customFormat="1"/>
+    <row r="399" customFormat="1"/>
+    <row r="400" customFormat="1"/>
+    <row r="401" customFormat="1"/>
+    <row r="402" customFormat="1"/>
+    <row r="403" customFormat="1"/>
+    <row r="404" customFormat="1"/>
+    <row r="405" customFormat="1"/>
+    <row r="406" customFormat="1"/>
+    <row r="407" customFormat="1"/>
+    <row r="408" customFormat="1"/>
+    <row r="409" customFormat="1"/>
+    <row r="410" customFormat="1"/>
+    <row r="411" customFormat="1"/>
+    <row r="412" customFormat="1"/>
+    <row r="413" customFormat="1"/>
+    <row r="414" customFormat="1"/>
+    <row r="415" customFormat="1"/>
+    <row r="416" customFormat="1"/>
+    <row r="417" customFormat="1"/>
+    <row r="418" customFormat="1"/>
+    <row r="419" customFormat="1"/>
+    <row r="420" customFormat="1"/>
+    <row r="421" customFormat="1"/>
+    <row r="422" customFormat="1"/>
+    <row r="423" customFormat="1"/>
+    <row r="424" customFormat="1"/>
+    <row r="425" customFormat="1"/>
+    <row r="426" customFormat="1"/>
+    <row r="427" customFormat="1"/>
+    <row r="428" customFormat="1"/>
+    <row r="429" customFormat="1"/>
+    <row r="430" customFormat="1"/>
+    <row r="431" customFormat="1"/>
+    <row r="432" customFormat="1"/>
+    <row r="433" customFormat="1"/>
+    <row r="434" customFormat="1"/>
+    <row r="435" customFormat="1"/>
+    <row r="436" customFormat="1"/>
+    <row r="437" customFormat="1"/>
+    <row r="438" customFormat="1"/>
+    <row r="439" customFormat="1"/>
+    <row r="440" customFormat="1"/>
+    <row r="441" customFormat="1"/>
+    <row r="442" customFormat="1"/>
+    <row r="443" customFormat="1"/>
+    <row r="444" customFormat="1"/>
+    <row r="445" customFormat="1"/>
+    <row r="446" customFormat="1"/>
+    <row r="447" customFormat="1"/>
+    <row r="448" customFormat="1"/>
+    <row r="449" customFormat="1"/>
+    <row r="450" customFormat="1"/>
+    <row r="451" customFormat="1"/>
+    <row r="452" customFormat="1"/>
+    <row r="453" customFormat="1"/>
+    <row r="454" customFormat="1"/>
+    <row r="455" customFormat="1"/>
+    <row r="456" customFormat="1"/>
+    <row r="457" customFormat="1"/>
+    <row r="458" customFormat="1"/>
+    <row r="459" customFormat="1"/>
+    <row r="460" customFormat="1"/>
+    <row r="461" customFormat="1"/>
+    <row r="462" customFormat="1"/>
+    <row r="463" customFormat="1"/>
+    <row r="464" customFormat="1"/>
+    <row r="465" customFormat="1"/>
+    <row r="466" customFormat="1"/>
+    <row r="467" customFormat="1"/>
+    <row r="468" customFormat="1"/>
+    <row r="469" customFormat="1"/>
+    <row r="470" customFormat="1"/>
+    <row r="471" customFormat="1"/>
+    <row r="472" customFormat="1"/>
+    <row r="473" customFormat="1"/>
+    <row r="474" customFormat="1"/>
+    <row r="475" customFormat="1"/>
+    <row r="476" customFormat="1"/>
+    <row r="477" customFormat="1"/>
+    <row r="478" customFormat="1"/>
+    <row r="479" customFormat="1"/>
+    <row r="480" customFormat="1"/>
+    <row r="481" customFormat="1"/>
+    <row r="482" customFormat="1"/>
+    <row r="483" customFormat="1"/>
+    <row r="484" customFormat="1"/>
+    <row r="485" customFormat="1"/>
+    <row r="486" customFormat="1"/>
+    <row r="487" customFormat="1"/>
+    <row r="488" customFormat="1"/>
+    <row r="489" customFormat="1"/>
+    <row r="490" customFormat="1"/>
+    <row r="491" customFormat="1"/>
+    <row r="492" customFormat="1"/>
+    <row r="493" customFormat="1"/>
+    <row r="494" customFormat="1"/>
+    <row r="495" customFormat="1"/>
+    <row r="496" customFormat="1"/>
+    <row r="497" customFormat="1"/>
+    <row r="498" customFormat="1"/>
+    <row r="499" customFormat="1"/>
+    <row r="500" customFormat="1"/>
+    <row r="501" customFormat="1"/>
+    <row r="502" customFormat="1"/>
+    <row r="503" customFormat="1"/>
+    <row r="504" customFormat="1"/>
+    <row r="505" customFormat="1"/>
+    <row r="506" customFormat="1"/>
+    <row r="507" customFormat="1"/>
+    <row r="508" customFormat="1"/>
+    <row r="509" customFormat="1"/>
+    <row r="510" customFormat="1"/>
+    <row r="511" customFormat="1"/>
+    <row r="512" customFormat="1"/>
+    <row r="513" customFormat="1"/>
+    <row r="514" customFormat="1"/>
+    <row r="515" customFormat="1"/>
+    <row r="516" customFormat="1"/>
+    <row r="517" customFormat="1"/>
+    <row r="518" customFormat="1"/>
+    <row r="519" customFormat="1"/>
+    <row r="520" customFormat="1"/>
+    <row r="521" customFormat="1"/>
+    <row r="522" customFormat="1"/>
+    <row r="523" customFormat="1"/>
+    <row r="524" customFormat="1"/>
+    <row r="525" customFormat="1"/>
+    <row r="526" customFormat="1"/>
+    <row r="527" customFormat="1"/>
+    <row r="528" customFormat="1"/>
+    <row r="529" customFormat="1"/>
+    <row r="530" customFormat="1"/>
+    <row r="531" customFormat="1"/>
+    <row r="532" customFormat="1"/>
+    <row r="533" customFormat="1"/>
+    <row r="534" customFormat="1"/>
+    <row r="535" customFormat="1"/>
+    <row r="536" customFormat="1"/>
+    <row r="537" customFormat="1"/>
+    <row r="538" customFormat="1"/>
+    <row r="539" customFormat="1"/>
+    <row r="540" customFormat="1"/>
+    <row r="541" customFormat="1"/>
+    <row r="542" customFormat="1"/>
+    <row r="543" customFormat="1"/>
+    <row r="544" customFormat="1"/>
+    <row r="545" customFormat="1"/>
+    <row r="546" customFormat="1"/>
+    <row r="547" customFormat="1"/>
+    <row r="548" customFormat="1"/>
+    <row r="549" customFormat="1"/>
+    <row r="550" customFormat="1"/>
+    <row r="551" customFormat="1"/>
+    <row r="552" customFormat="1"/>
+    <row r="553" customFormat="1"/>
+    <row r="554" customFormat="1"/>
+    <row r="555" customFormat="1"/>
+    <row r="556" customFormat="1"/>
+    <row r="557" customFormat="1"/>
+    <row r="558" customFormat="1"/>
+    <row r="559" customFormat="1"/>
+    <row r="560" customFormat="1"/>
+    <row r="561" customFormat="1"/>
+    <row r="562" customFormat="1"/>
+    <row r="563" customFormat="1"/>
+    <row r="564" customFormat="1"/>
+    <row r="565" customFormat="1"/>
+    <row r="566" customFormat="1"/>
+    <row r="567" customFormat="1"/>
+    <row r="568" customFormat="1"/>
+    <row r="569" customFormat="1"/>
+    <row r="570" customFormat="1"/>
+    <row r="571" customFormat="1"/>
+    <row r="572" customFormat="1"/>
+    <row r="573" customFormat="1"/>
+    <row r="574" customFormat="1"/>
+    <row r="575" customFormat="1"/>
+    <row r="576" customFormat="1"/>
+    <row r="577" customFormat="1"/>
+    <row r="578" customFormat="1"/>
+    <row r="579" customFormat="1"/>
+    <row r="580" customFormat="1"/>
+    <row r="581" customFormat="1"/>
+    <row r="582" customFormat="1"/>
+    <row r="583" customFormat="1"/>
+    <row r="584" customFormat="1"/>
+    <row r="585" customFormat="1"/>
+    <row r="586" customFormat="1"/>
+    <row r="587" customFormat="1"/>
+    <row r="588" customFormat="1"/>
+    <row r="589" customFormat="1"/>
+    <row r="590" customFormat="1"/>
+    <row r="591" customFormat="1"/>
+    <row r="592" customFormat="1"/>
+    <row r="593" customFormat="1"/>
+    <row r="594" customFormat="1"/>
+    <row r="595" customFormat="1"/>
+    <row r="596" customFormat="1"/>
+    <row r="597" customFormat="1"/>
+    <row r="598" customFormat="1"/>
+    <row r="599" customFormat="1"/>
+    <row r="600" customFormat="1"/>
+    <row r="601" customFormat="1"/>
+    <row r="602" customFormat="1"/>
+    <row r="603" customFormat="1"/>
+    <row r="604" customFormat="1"/>
+    <row r="605" customFormat="1"/>
+    <row r="606" customFormat="1"/>
+    <row r="607" customFormat="1"/>
+    <row r="608" customFormat="1"/>
+    <row r="609" customFormat="1"/>
+    <row r="610" customFormat="1"/>
+    <row r="611" customFormat="1"/>
+    <row r="612" customFormat="1"/>
+    <row r="613" customFormat="1"/>
+    <row r="614" customFormat="1"/>
+    <row r="615" customFormat="1"/>
+    <row r="616" customFormat="1"/>
+    <row r="617" customFormat="1"/>
+    <row r="618" customFormat="1"/>
+    <row r="619" customFormat="1"/>
+    <row r="620" customFormat="1"/>
+    <row r="621" customFormat="1"/>
+    <row r="622" customFormat="1"/>
+    <row r="623" customFormat="1"/>
+    <row r="624" customFormat="1"/>
+    <row r="625" customFormat="1"/>
+    <row r="626" customFormat="1"/>
+    <row r="627" customFormat="1"/>
+    <row r="628" customFormat="1"/>
+    <row r="629" customFormat="1"/>
+    <row r="630" customFormat="1"/>
+    <row r="631" customFormat="1"/>
+    <row r="632" customFormat="1"/>
+    <row r="633" customFormat="1"/>
+    <row r="634" customFormat="1"/>
+    <row r="635" customFormat="1"/>
+    <row r="636" customFormat="1"/>
+    <row r="637" customFormat="1"/>
+    <row r="638" customFormat="1"/>
+    <row r="639" customFormat="1"/>
+    <row r="640" customFormat="1"/>
+    <row r="641" customFormat="1"/>
+    <row r="642" customFormat="1"/>
+    <row r="643" customFormat="1"/>
+    <row r="644" customFormat="1"/>
+    <row r="645" customFormat="1"/>
+    <row r="646" customFormat="1"/>
+    <row r="647" customFormat="1"/>
+    <row r="648" customFormat="1"/>
+    <row r="649" customFormat="1"/>
+    <row r="650" customFormat="1"/>
+    <row r="651" customFormat="1"/>
+    <row r="652" customFormat="1"/>
+    <row r="653" customFormat="1"/>
+    <row r="654" customFormat="1"/>
+    <row r="655" customFormat="1"/>
+    <row r="656" customFormat="1"/>
+    <row r="657" customFormat="1"/>
+    <row r="658" customFormat="1"/>
+    <row r="659" customFormat="1"/>
+    <row r="660" customFormat="1"/>
+    <row r="661" customFormat="1"/>
+    <row r="662" customFormat="1"/>
+    <row r="663" customFormat="1"/>
+    <row r="664" customFormat="1"/>
+    <row r="665" customFormat="1"/>
+    <row r="666" customFormat="1"/>
+    <row r="667" customFormat="1"/>
+    <row r="668" customFormat="1"/>
+    <row r="669" customFormat="1"/>
+    <row r="670" customFormat="1"/>
+    <row r="671" customFormat="1"/>
+    <row r="672" customFormat="1"/>
+    <row r="673" customFormat="1"/>
+    <row r="674" customFormat="1"/>
+    <row r="675" customFormat="1"/>
+    <row r="676" customFormat="1"/>
+    <row r="677" customFormat="1"/>
+    <row r="678" customFormat="1"/>
+    <row r="679" customFormat="1"/>
+    <row r="680" customFormat="1"/>
+    <row r="681" customFormat="1"/>
+    <row r="682" customFormat="1"/>
+    <row r="683" customFormat="1"/>
+    <row r="684" customFormat="1"/>
+    <row r="685" customFormat="1"/>
+    <row r="686" customFormat="1"/>
+    <row r="687" customFormat="1"/>
+    <row r="688" customFormat="1"/>
+    <row r="689" customFormat="1"/>
+    <row r="690" customFormat="1"/>
+    <row r="691" customFormat="1"/>
+    <row r="692" customFormat="1"/>
+    <row r="693" customFormat="1"/>
+    <row r="694" customFormat="1"/>
+    <row r="695" customFormat="1"/>
+    <row r="696" customFormat="1"/>
+    <row r="697" customFormat="1"/>
+    <row r="698" customFormat="1"/>
+    <row r="699" customFormat="1"/>
+    <row r="700" customFormat="1"/>
+    <row r="701" customFormat="1"/>
+    <row r="702" customFormat="1"/>
+    <row r="703" customFormat="1"/>
+    <row r="704" customFormat="1"/>
+    <row r="705" customFormat="1"/>
+    <row r="706" customFormat="1"/>
+    <row r="707" customFormat="1"/>
+    <row r="708" customFormat="1"/>
+    <row r="709" customFormat="1"/>
+    <row r="710" customFormat="1"/>
+    <row r="711" customFormat="1"/>
+    <row r="712" customFormat="1"/>
+    <row r="713" customFormat="1"/>
+    <row r="714" customFormat="1"/>
+    <row r="715" customFormat="1"/>
+    <row r="716" customFormat="1"/>
+    <row r="717" customFormat="1"/>
+    <row r="718" customFormat="1"/>
+    <row r="719" customFormat="1"/>
+    <row r="720" customFormat="1"/>
+    <row r="721" customFormat="1"/>
+    <row r="722" customFormat="1"/>
+    <row r="723" customFormat="1"/>
+    <row r="724" customFormat="1"/>
+    <row r="725" customFormat="1"/>
+    <row r="726" customFormat="1"/>
+    <row r="727" customFormat="1"/>
+    <row r="728" customFormat="1"/>
+    <row r="729" customFormat="1"/>
+    <row r="730" customFormat="1"/>
+    <row r="731" customFormat="1"/>
+    <row r="732" customFormat="1"/>
+    <row r="733" customFormat="1"/>
+    <row r="734" customFormat="1"/>
+    <row r="735" customFormat="1"/>
+    <row r="736" customFormat="1"/>
+    <row r="737" customFormat="1"/>
+    <row r="738" customFormat="1"/>
+    <row r="739" customFormat="1"/>
+    <row r="740" customFormat="1"/>
+    <row r="741" customFormat="1"/>
+    <row r="742" customFormat="1"/>
+    <row r="743" customFormat="1"/>
+    <row r="744" customFormat="1"/>
+    <row r="745" customFormat="1"/>
+    <row r="746" customFormat="1"/>
+    <row r="747" customFormat="1"/>
+    <row r="748" customFormat="1"/>
+    <row r="749" customFormat="1"/>
+    <row r="750" customFormat="1"/>
+    <row r="751" customFormat="1"/>
+    <row r="752" customFormat="1"/>
+    <row r="753" customFormat="1"/>
+    <row r="754" customFormat="1"/>
+    <row r="755" customFormat="1"/>
+    <row r="756" customFormat="1"/>
+    <row r="757" customFormat="1"/>
+    <row r="758" customFormat="1"/>
+    <row r="759" customFormat="1"/>
+    <row r="760" customFormat="1"/>
+    <row r="761" customFormat="1"/>
+    <row r="762" customFormat="1"/>
+    <row r="763" customFormat="1"/>
+    <row r="764" customFormat="1"/>
+    <row r="765" customFormat="1"/>
+    <row r="766" customFormat="1"/>
+    <row r="767" customFormat="1"/>
+    <row r="768" customFormat="1"/>
+    <row r="769" customFormat="1"/>
+    <row r="770" customFormat="1"/>
+    <row r="771" customFormat="1"/>
+    <row r="772" customFormat="1"/>
+    <row r="773" customFormat="1"/>
+    <row r="774" customFormat="1"/>
+    <row r="775" customFormat="1"/>
+    <row r="776" customFormat="1"/>
+    <row r="777" customFormat="1"/>
+    <row r="778" customFormat="1"/>
+    <row r="779" customFormat="1"/>
+    <row r="780" customFormat="1"/>
+    <row r="781" customFormat="1"/>
+    <row r="782" customFormat="1"/>
+    <row r="783" customFormat="1"/>
+    <row r="784" customFormat="1"/>
+    <row r="785" customFormat="1"/>
+    <row r="786" customFormat="1"/>
+    <row r="787" customFormat="1"/>
+    <row r="788" customFormat="1"/>
+    <row r="789" customFormat="1"/>
+    <row r="790" customFormat="1"/>
+    <row r="791" customFormat="1"/>
+    <row r="792" customFormat="1"/>
+    <row r="793" customFormat="1"/>
+    <row r="794" customFormat="1"/>
+    <row r="795" customFormat="1"/>
+    <row r="796" customFormat="1"/>
+    <row r="797" customFormat="1"/>
+    <row r="798" customFormat="1"/>
+    <row r="799" customFormat="1"/>
+    <row r="800" customFormat="1"/>
+    <row r="801" customFormat="1"/>
+    <row r="802" customFormat="1"/>
+    <row r="803" customFormat="1"/>
+    <row r="804" customFormat="1"/>
+    <row r="805" customFormat="1"/>
+    <row r="806" customFormat="1"/>
+    <row r="807" customFormat="1"/>
+    <row r="808" customFormat="1"/>
+    <row r="809" customFormat="1"/>
+    <row r="810" customFormat="1"/>
+    <row r="811" customFormat="1"/>
+    <row r="812" customFormat="1"/>
+    <row r="813" customFormat="1"/>
+    <row r="814" customFormat="1"/>
+    <row r="815" customFormat="1"/>
+    <row r="816" customFormat="1"/>
+    <row r="817" customFormat="1"/>
+    <row r="818" customFormat="1"/>
+    <row r="819" customFormat="1"/>
+    <row r="820" customFormat="1"/>
+    <row r="821" customFormat="1"/>
+    <row r="822" customFormat="1"/>
+    <row r="823" customFormat="1"/>
+    <row r="824" customFormat="1"/>
+    <row r="825" customFormat="1"/>
+    <row r="826" customFormat="1"/>
+    <row r="827" customFormat="1"/>
+    <row r="828" customFormat="1"/>
+    <row r="829" customFormat="1"/>
+    <row r="830" customFormat="1"/>
+    <row r="831" customFormat="1"/>
+    <row r="832" customFormat="1"/>
+    <row r="833" customFormat="1"/>
+    <row r="834" customFormat="1"/>
+    <row r="835" customFormat="1"/>
+    <row r="836" customFormat="1"/>
+    <row r="837" customFormat="1"/>
+    <row r="838" customFormat="1"/>
+    <row r="839" customFormat="1"/>
+    <row r="840" customFormat="1"/>
+    <row r="841" customFormat="1"/>
+    <row r="842" customFormat="1"/>
+    <row r="843" customFormat="1"/>
+    <row r="844" customFormat="1"/>
+    <row r="845" customFormat="1"/>
+    <row r="846" customFormat="1"/>
+    <row r="847" customFormat="1"/>
+    <row r="848" customFormat="1"/>
+    <row r="849" customFormat="1"/>
+    <row r="850" customFormat="1"/>
+    <row r="851" customFormat="1"/>
+    <row r="852" customFormat="1"/>
+    <row r="853" customFormat="1"/>
+    <row r="854" customFormat="1"/>
+    <row r="855" customFormat="1"/>
+    <row r="856" customFormat="1"/>
+    <row r="857" customFormat="1"/>
+    <row r="858" customFormat="1"/>
+    <row r="859" customFormat="1"/>
+    <row r="860" customFormat="1"/>
+    <row r="861" customFormat="1"/>
+    <row r="862" customFormat="1"/>
+    <row r="863" customFormat="1"/>
+    <row r="864" customFormat="1"/>
+    <row r="865" customFormat="1"/>
+    <row r="866" customFormat="1"/>
+    <row r="867" customFormat="1"/>
+    <row r="868" customFormat="1"/>
+    <row r="869" customFormat="1"/>
+    <row r="870" customFormat="1"/>
+    <row r="871" customFormat="1"/>
+    <row r="872" customFormat="1"/>
+    <row r="873" customFormat="1"/>
+    <row r="874" customFormat="1"/>
+    <row r="875" customFormat="1"/>
+    <row r="876" customFormat="1"/>
+    <row r="877" customFormat="1"/>
+    <row r="878" customFormat="1"/>
+    <row r="879" customFormat="1"/>
+    <row r="880" customFormat="1"/>
+    <row r="881" customFormat="1"/>
+    <row r="882" customFormat="1"/>
+    <row r="883" customFormat="1"/>
+    <row r="884" customFormat="1"/>
+    <row r="885" customFormat="1"/>
+    <row r="886" customFormat="1"/>
+    <row r="887" customFormat="1"/>
+    <row r="888" customFormat="1"/>
+    <row r="889" customFormat="1"/>
+    <row r="890" customFormat="1"/>
+    <row r="891" customFormat="1"/>
+    <row r="892" customFormat="1"/>
+    <row r="893" customFormat="1"/>
+    <row r="894" customFormat="1"/>
+    <row r="895" customFormat="1"/>
+    <row r="896" customFormat="1"/>
+    <row r="897" customFormat="1"/>
+    <row r="898" customFormat="1"/>
+    <row r="899" customFormat="1"/>
+    <row r="900" customFormat="1"/>
+    <row r="901" customFormat="1"/>
+    <row r="902" customFormat="1"/>
+    <row r="903" customFormat="1"/>
+    <row r="904" customFormat="1"/>
+    <row r="905" customFormat="1"/>
+    <row r="906" customFormat="1"/>
+    <row r="907" customFormat="1"/>
+    <row r="908" customFormat="1"/>
+    <row r="909" customFormat="1"/>
+    <row r="910" customFormat="1"/>
+    <row r="911" customFormat="1"/>
+    <row r="912" customFormat="1"/>
+    <row r="913" customFormat="1"/>
+    <row r="914" customFormat="1"/>
+    <row r="915" customFormat="1"/>
+    <row r="916" customFormat="1"/>
+    <row r="917" customFormat="1"/>
+    <row r="918" customFormat="1"/>
+    <row r="919" customFormat="1"/>
+    <row r="920" customFormat="1"/>
+    <row r="921" customFormat="1"/>
+    <row r="922" customFormat="1"/>
+    <row r="923" customFormat="1"/>
+    <row r="924" customFormat="1"/>
+    <row r="925" customFormat="1"/>
+    <row r="926" customFormat="1"/>
+    <row r="927" customFormat="1"/>
+    <row r="928" customFormat="1"/>
+    <row r="929" customFormat="1"/>
+    <row r="930" customFormat="1"/>
+    <row r="931" customFormat="1"/>
+    <row r="932" customFormat="1"/>
+    <row r="933" customFormat="1"/>
+    <row r="934" customFormat="1"/>
+    <row r="935" customFormat="1"/>
+    <row r="936" customFormat="1"/>
+    <row r="937" customFormat="1"/>
+    <row r="938" customFormat="1"/>
+    <row r="939" customFormat="1"/>
+    <row r="940" customFormat="1"/>
+    <row r="941" customFormat="1"/>
+    <row r="942" customFormat="1"/>
+    <row r="943" customFormat="1"/>
+    <row r="944" customFormat="1"/>
+    <row r="945" customFormat="1"/>
+    <row r="946" customFormat="1"/>
+    <row r="947" customFormat="1"/>
+    <row r="948" customFormat="1"/>
+    <row r="949" customFormat="1"/>
+    <row r="950" customFormat="1"/>
+    <row r="951" customFormat="1"/>
+    <row r="952" customFormat="1"/>
+    <row r="953" customFormat="1"/>
+    <row r="954" customFormat="1"/>
+    <row r="955" customFormat="1"/>
+    <row r="956" customFormat="1"/>
+    <row r="957" customFormat="1"/>
+    <row r="958" customFormat="1"/>
+    <row r="959" customFormat="1"/>
+    <row r="960" customFormat="1"/>
+    <row r="961" customFormat="1"/>
+    <row r="962" customFormat="1"/>
+    <row r="963" customFormat="1"/>
+    <row r="964" customFormat="1"/>
+    <row r="965" customFormat="1"/>
+    <row r="966" customFormat="1"/>
+    <row r="967" customFormat="1"/>
+    <row r="968" customFormat="1"/>
+    <row r="969" customFormat="1"/>
+    <row r="970" customFormat="1"/>
+    <row r="971" customFormat="1"/>
+    <row r="972" customFormat="1"/>
+    <row r="973" customFormat="1"/>
+    <row r="974" customFormat="1"/>
+    <row r="975" customFormat="1"/>
+    <row r="976" customFormat="1"/>
+    <row r="977" customFormat="1"/>
+    <row r="978" customFormat="1"/>
+    <row r="979" customFormat="1"/>
+    <row r="980" customFormat="1"/>
+    <row r="981" customFormat="1"/>
+    <row r="982" customFormat="1"/>
+    <row r="983" customFormat="1"/>
+    <row r="984" customFormat="1"/>
+    <row r="985" customFormat="1"/>
+    <row r="986" customFormat="1"/>
+    <row r="987" customFormat="1"/>
+    <row r="988" customFormat="1"/>
+    <row r="989" customFormat="1"/>
+    <row r="990" customFormat="1"/>
+    <row r="991" customFormat="1"/>
+    <row r="992" customFormat="1"/>
+    <row r="993" customFormat="1"/>
+    <row r="994" customFormat="1"/>
+    <row r="995" customFormat="1"/>
+    <row r="996" customFormat="1"/>
+    <row r="997" customFormat="1"/>
+    <row r="998" customFormat="1"/>
+    <row r="999" customFormat="1"/>
+    <row r="1000" customFormat="1"/>
+    <row r="1001" customFormat="1"/>
+    <row r="1002" customFormat="1"/>
+    <row r="1003" customFormat="1"/>
+    <row r="1004" customFormat="1"/>
+    <row r="1005" customFormat="1"/>
+    <row r="1006" customFormat="1"/>
+    <row r="1007" customFormat="1"/>
+    <row r="1008" customFormat="1"/>
+    <row r="1009" customFormat="1"/>
+    <row r="1010" customFormat="1"/>
+    <row r="1011" customFormat="1"/>
+    <row r="1012" customFormat="1"/>
+    <row r="1013" customFormat="1"/>
+    <row r="1014" customFormat="1"/>
+    <row r="1015" customFormat="1"/>
+    <row r="1016" customFormat="1"/>
+    <row r="1017" customFormat="1"/>
+    <row r="1018" customFormat="1"/>
+    <row r="1019" customFormat="1"/>
+    <row r="1020" customFormat="1"/>
+    <row r="1021" customFormat="1"/>
+    <row r="1022" customFormat="1"/>
+    <row r="1023" customFormat="1"/>
+    <row r="1024" customFormat="1"/>
+    <row r="1025" customFormat="1"/>
+    <row r="1026" customFormat="1"/>
+    <row r="1027" customFormat="1"/>
+    <row r="1028" customFormat="1"/>
+    <row r="1029" customFormat="1"/>
+    <row r="1030" customFormat="1"/>
+    <row r="1031" customFormat="1"/>
+    <row r="1032" customFormat="1"/>
+    <row r="1033" customFormat="1"/>
+    <row r="1034" customFormat="1"/>
+    <row r="1035" customFormat="1"/>
+    <row r="1036" customFormat="1"/>
+    <row r="1037" customFormat="1"/>
+    <row r="1038" customFormat="1"/>
+    <row r="1039" customFormat="1"/>
+    <row r="1040" customFormat="1"/>
+    <row r="1041" customFormat="1"/>
+    <row r="1042" customFormat="1"/>
+    <row r="1043" customFormat="1"/>
+    <row r="1044" customFormat="1"/>
+    <row r="1045" customFormat="1"/>
+    <row r="1046" customFormat="1"/>
+    <row r="1047" customFormat="1"/>
+    <row r="1048" customFormat="1"/>
+    <row r="1049" customFormat="1"/>
+    <row r="1050" customFormat="1"/>
+    <row r="1051" customFormat="1"/>
+    <row r="1052" customFormat="1"/>
+    <row r="1053" customFormat="1"/>
+    <row r="1054" customFormat="1"/>
+    <row r="1055" customFormat="1"/>
+    <row r="1056" customFormat="1"/>
+    <row r="1057" customFormat="1"/>
+    <row r="1058" customFormat="1"/>
+    <row r="1059" customFormat="1"/>
+    <row r="1060" customFormat="1"/>
+    <row r="1061" customFormat="1"/>
+    <row r="1062" customFormat="1"/>
+    <row r="1063" customFormat="1"/>
+    <row r="1064" customFormat="1"/>
+    <row r="1065" customFormat="1"/>
+    <row r="1066" customFormat="1"/>
+    <row r="1067" customFormat="1"/>
+    <row r="1068" customFormat="1"/>
+    <row r="1069" customFormat="1"/>
+    <row r="1070" customFormat="1"/>
+    <row r="1071" customFormat="1"/>
+    <row r="1072" customFormat="1"/>
+    <row r="1073" customFormat="1"/>
+    <row r="1074" customFormat="1"/>
+    <row r="1075" customFormat="1"/>
+    <row r="1076" customFormat="1"/>
+    <row r="1077" customFormat="1"/>
+    <row r="1078" customFormat="1"/>
+    <row r="1079" customFormat="1"/>
+    <row r="1080" customFormat="1"/>
+    <row r="1081" customFormat="1"/>
+    <row r="1082" customFormat="1"/>
+    <row r="1083" customFormat="1"/>
+    <row r="1084" customFormat="1"/>
+    <row r="1085" customFormat="1"/>
+    <row r="1086" customFormat="1"/>
+    <row r="1087" customFormat="1"/>
+    <row r="1088" customFormat="1"/>
+    <row r="1089" customFormat="1"/>
+    <row r="1090" customFormat="1"/>
+    <row r="1091" customFormat="1"/>
+    <row r="1092" customFormat="1"/>
+    <row r="1093" customFormat="1"/>
+    <row r="1094" customFormat="1"/>
+    <row r="1095" customFormat="1"/>
+    <row r="1096" customFormat="1"/>
+    <row r="1097" customFormat="1"/>
+    <row r="1098" customFormat="1"/>
+    <row r="1099" customFormat="1"/>
+    <row r="1100" customFormat="1"/>
+    <row r="1101" customFormat="1"/>
+    <row r="1102" customFormat="1"/>
+    <row r="1103" customFormat="1"/>
+    <row r="1104" customFormat="1"/>
+    <row r="1105" customFormat="1"/>
+    <row r="1106" customFormat="1"/>
+    <row r="1107" customFormat="1"/>
+    <row r="1108" customFormat="1"/>
+    <row r="1109" customFormat="1"/>
+    <row r="1110" customFormat="1"/>
+    <row r="1111" customFormat="1"/>
+    <row r="1112" customFormat="1"/>
+    <row r="1113" customFormat="1"/>
+    <row r="1114" customFormat="1"/>
+    <row r="1115" customFormat="1"/>
+    <row r="1116" customFormat="1"/>
+    <row r="1117" customFormat="1"/>
+    <row r="1118" customFormat="1"/>
+    <row r="1119" customFormat="1"/>
+    <row r="1120" customFormat="1"/>
+    <row r="1121" customFormat="1"/>
+    <row r="1122" customFormat="1"/>
+    <row r="1123" customFormat="1"/>
+    <row r="1124" customFormat="1"/>
+    <row r="1125" customFormat="1"/>
+    <row r="1126" customFormat="1"/>
+    <row r="1127" customFormat="1"/>
+    <row r="1128" customFormat="1"/>
+    <row r="1129" customFormat="1"/>
+    <row r="1130" customFormat="1"/>
+    <row r="1131" customFormat="1"/>
+    <row r="1132" customFormat="1"/>
+    <row r="1133" customFormat="1"/>
+    <row r="1134" customFormat="1"/>
+    <row r="1135" customFormat="1"/>
+    <row r="1136" customFormat="1"/>
+    <row r="1137" customFormat="1"/>
+    <row r="1138" customFormat="1"/>
+    <row r="1139" customFormat="1"/>
+    <row r="1140" customFormat="1"/>
+    <row r="1141" customFormat="1"/>
+    <row r="1142" customFormat="1"/>
+    <row r="1143" customFormat="1"/>
+    <row r="1144" customFormat="1"/>
+    <row r="1145" customFormat="1"/>
+    <row r="1146" customFormat="1"/>
+    <row r="1147" customFormat="1"/>
+    <row r="1148" customFormat="1"/>
+    <row r="1149" customFormat="1"/>
+    <row r="1150" customFormat="1"/>
+    <row r="1151" customFormat="1"/>
+    <row r="1152" customFormat="1"/>
+    <row r="1153" customFormat="1"/>
+    <row r="1154" customFormat="1"/>
+    <row r="1155" customFormat="1"/>
+    <row r="1156" customFormat="1"/>
+    <row r="1157" customFormat="1"/>
+    <row r="1158" customFormat="1"/>
+    <row r="1159" customFormat="1"/>
+    <row r="1160" customFormat="1"/>
+    <row r="1161" customFormat="1"/>
+    <row r="1162" customFormat="1"/>
+    <row r="1163" customFormat="1"/>
+    <row r="1164" customFormat="1"/>
+    <row r="1165" customFormat="1"/>
+    <row r="1166" customFormat="1"/>
+    <row r="1167" customFormat="1"/>
+    <row r="1168" customFormat="1"/>
+    <row r="1169" customFormat="1"/>
+    <row r="1170" customFormat="1"/>
+    <row r="1171" customFormat="1"/>
+    <row r="1172" customFormat="1"/>
+    <row r="1173" customFormat="1"/>
+    <row r="1174" customFormat="1"/>
+    <row r="1175" customFormat="1"/>
+    <row r="1176" customFormat="1"/>
+    <row r="1177" customFormat="1"/>
+    <row r="1178" customFormat="1"/>
+    <row r="1179" customFormat="1"/>
+    <row r="1180" customFormat="1"/>
+    <row r="1181" customFormat="1"/>
+    <row r="1182" customFormat="1"/>
+    <row r="1183" customFormat="1"/>
+    <row r="1184" customFormat="1"/>
+    <row r="1185" customFormat="1"/>
+    <row r="1186" customFormat="1"/>
+    <row r="1187" customFormat="1"/>
+    <row r="1188" customFormat="1"/>
+    <row r="1189" customFormat="1"/>
+    <row r="1190" customFormat="1"/>
+    <row r="1191" customFormat="1"/>
+    <row r="1192" customFormat="1"/>
+    <row r="1193" customFormat="1"/>
+    <row r="1194" customFormat="1"/>
+    <row r="1195" customFormat="1"/>
+    <row r="1196" customFormat="1"/>
+    <row r="1197" customFormat="1"/>
+    <row r="1198" customFormat="1"/>
+    <row r="1199" customFormat="1"/>
+    <row r="1200" customFormat="1"/>
+    <row r="1201" customFormat="1"/>
+    <row r="1202" customFormat="1"/>
+    <row r="1203" customFormat="1"/>
+    <row r="1204" customFormat="1"/>
+    <row r="1205" customFormat="1"/>
+    <row r="1206" customFormat="1"/>
+    <row r="1207" customFormat="1"/>
+    <row r="1208" customFormat="1"/>
+    <row r="1209" customFormat="1"/>
+    <row r="1210" customFormat="1"/>
+    <row r="1211" customFormat="1"/>
+    <row r="1212" customFormat="1"/>
+    <row r="1213" customFormat="1"/>
+    <row r="1214" customFormat="1"/>
+    <row r="1215" customFormat="1"/>
+    <row r="1216" customFormat="1"/>
+    <row r="1217" customFormat="1"/>
+    <row r="1218" customFormat="1"/>
+    <row r="1219" customFormat="1"/>
+    <row r="1220" customFormat="1"/>
+    <row r="1221" customFormat="1"/>
+    <row r="1222" customFormat="1"/>
+    <row r="1223" customFormat="1"/>
+    <row r="1224" customFormat="1"/>
+    <row r="1225" customFormat="1"/>
+    <row r="1226" customFormat="1"/>
+    <row r="1227" customFormat="1"/>
+    <row r="1228" customFormat="1"/>
+    <row r="1229" customFormat="1"/>
+    <row r="1230" customFormat="1"/>
+    <row r="1231" customFormat="1"/>
+    <row r="1232" customFormat="1"/>
+    <row r="1233" customFormat="1"/>
+    <row r="1234" customFormat="1"/>
+    <row r="1235" customFormat="1"/>
+    <row r="1236" customFormat="1"/>
+    <row r="1237" customFormat="1"/>
+    <row r="1238" customFormat="1"/>
+    <row r="1239" customFormat="1"/>
+    <row r="1240" customFormat="1"/>
+    <row r="1241" customFormat="1"/>
+    <row r="1242" customFormat="1"/>
+    <row r="1243" customFormat="1"/>
+    <row r="1244" customFormat="1"/>
+    <row r="1245" customFormat="1"/>
+    <row r="1246" customFormat="1"/>
+    <row r="1247" customFormat="1"/>
+    <row r="1248" customFormat="1"/>
+    <row r="1249" customFormat="1"/>
+    <row r="1250" customFormat="1"/>
+    <row r="1251" customFormat="1"/>
+    <row r="1252" customFormat="1"/>
+    <row r="1701" customFormat="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
